--- a/output/pdf_financials_xlsx/AWM.xlsx
+++ b/output/pdf_financials_xlsx/AWM.xlsx
@@ -4489,25 +4489,25 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.633015</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.186716</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.158949</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.207058</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.207058</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.207058</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.207058</v>
       </c>
       <c r="I92" s="3" t="n">
         <v>3.348908</v>
@@ -11264,7 +11264,11 @@
           <t>Share based payment reserve</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -12004,7 +12008,11 @@
           <t>Share based payment reserve</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E71" s="5" t="n">
         <v>0.633015</v>
       </c>

--- a/output/pdf_financials_xlsx/AWM.xlsx
+++ b/output/pdf_financials_xlsx/AWM.xlsx
@@ -1891,22 +1891,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.633193</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.31382</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.469415</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.33964</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.08730599999999999</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.427345</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>1.14415</v>
@@ -1915,7 +1915,7 @@
         <v>5.75872</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.269484</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>2.213578</v>
@@ -1977,22 +1977,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.633193</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.31382</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.469415</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.33964</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.08730599999999999</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.427345</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>1.14415</v>
@@ -2001,7 +2001,7 @@
         <v>8.767847</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>2.517085</v>
+        <v>2.786569</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>2.213578</v>
@@ -2493,22 +2493,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.888357</v>
+        <v>0.255164</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.3377</v>
+        <v>0.02388</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.474297</v>
+        <v>0.004882</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.34476</v>
+        <v>0.00512</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.09235400000000001</v>
+        <v>0.005048</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.427347</v>
+        <v>2e-06</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.18621</v>
@@ -2517,7 +2517,7 @@
         <v>0.107562</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.177811</v>
+        <v>0.908327</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0.006426</v>
@@ -8350,7 +8350,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">

--- a/output/pdf_financials_xlsx/AWM.xlsx
+++ b/output/pdf_financials_xlsx/AWM.xlsx
@@ -5432,13 +5432,13 @@
         <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.384006</v>
       </c>
       <c r="D112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.1185</v>
       </c>
       <c r="F112" s="3" t="n">
         <v>0</v>
@@ -17418,7 +17418,11 @@
           <t>Proceeds on disposition of property and equipment</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/AWM.xlsx
+++ b/output/pdf_financials_xlsx/AWM.xlsx
@@ -1115,7 +1115,7 @@
         <v>-0</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0.033843</v>
+        <v>-0.033843</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>-0.323275</v>
@@ -1283,7 +1283,7 @@
         <v>-0.523923</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-0.015138</v>
+        <v>-0.300427</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>-0.182357</v>
@@ -1292,16 +1292,16 @@
         <v>-0.176913</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>-0.012364</v>
+        <v>-1.918031</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.03619</v>
+        <v>-7.017214</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>-0.012612</v>
+        <v>-3.773562</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>-2.169513</v>
+        <v>-2.075925</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>-1.559712</v>
@@ -1320,13 +1320,13 @@
         <v>0</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0</v>
+        <v>-0.018607</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0</v>
+        <v>0.098784</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0</v>
+        <v>-0.015138</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>0</v>
@@ -13874,7 +13874,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
@@ -20214,7 +20218,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>
@@ -21188,11 +21196,7 @@
           <t>Net (loss) income from discontinuing operations (note 5)</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>NetIncomeContinuousOperations</t>
-        </is>
-      </c>
+      <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
@@ -21798,7 +21802,11 @@
           <t>Deferred income tax recovery (note 14)</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>-</t>
@@ -21872,11 +21880,7 @@
           <t>Net income (loss) from discontinuing operations (note 8)</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>NetIncomeContinuousOperations</t>
-        </is>
-      </c>
+      <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -24100,7 +24104,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -24176,7 +24184,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>NetIncomeContinuousOperations</t>
+          <t>NetIncomeDiscontinuousOperations</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -24828,7 +24836,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -24902,7 +24914,11 @@
           <t>Net income (loss) from discontinued operation 15</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>
